--- a/vtiger.crm/src/test/resources/testcase.xlsx
+++ b/vtiger.crm/src/test/resources/testcase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sprint_vtiger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39514B9D-42A3-4243-A5BB-3CE4DF711526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A9026C-875D-447D-8401-392435761DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8444B2F-1C6D-467C-A1CF-0AC616A96504}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B8444B2F-1C6D-467C-A1CF-0AC616A96504}"/>
   </bookViews>
   <sheets>
     <sheet name="opportunities" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>salesstage</t>
   </si>
@@ -184,21 +184,12 @@
     <t>sample.pdf</t>
   </si>
   <si>
-    <t>F1</t>
-  </si>
-  <si>
     <t>subject</t>
   </si>
   <si>
     <t>msg</t>
   </si>
   <si>
-    <t>to</t>
-  </si>
-  <si>
-    <t>Mukesh</t>
-  </si>
-  <si>
     <t>qa.cc@example.com</t>
   </si>
   <si>
@@ -211,27 +202,15 @@
     <t>Testing CC and BCC recipients</t>
   </si>
   <si>
-    <t>Vinayak Malgaund</t>
-  </si>
-  <si>
     <t>cc</t>
   </si>
   <si>
     <t>bcc</t>
   </si>
   <si>
-    <t>I1</t>
-  </si>
-  <si>
-    <t>Hello I am som</t>
-  </si>
-  <si>
     <t>docname</t>
   </si>
   <si>
-    <t>N1</t>
-  </si>
-  <si>
     <t>test.cc@example.com</t>
   </si>
   <si>
@@ -251,6 +230,42 @@
   </si>
   <si>
     <t>Probabilty</t>
+  </si>
+  <si>
+    <t>kenche Sowmya</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>Kenche</t>
+  </si>
+  <si>
+    <t>contact name</t>
+  </si>
+  <si>
+    <t>aish@gmail.com</t>
+  </si>
+  <si>
+    <t>anu@gmail.com</t>
+  </si>
+  <si>
+    <t>sending the doc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hi how are you </t>
+  </si>
+  <si>
+    <t>aafi@gmail.com</t>
+  </si>
+  <si>
+    <t>medha@gmail.com</t>
+  </si>
+  <si>
+    <t>Mailntact Mail</t>
+  </si>
+  <si>
+    <t>manual test cases</t>
   </si>
 </sst>
 </file>
@@ -656,7 +671,7 @@
         <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -823,87 +838,105 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" t="s">
-        <v>53</v>
-      </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" t="s">
-        <v>50</v>
+        <v>67</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>67</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
         <v>50</v>
@@ -911,10 +944,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{36AAA472-11E1-498E-AF44-6801FAFAAE77}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{1F6F97DD-DE2B-4C03-88A2-B816C01ED719}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{36AAA472-11E1-498E-AF44-6801FAFAAE77}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{1F6F97DD-DE2B-4C03-88A2-B816C01ED719}"/>
     <hyperlink ref="D5" r:id="rId3" xr:uid="{1D901955-5BE4-480C-8724-D8CB9C6ECB9B}"/>
     <hyperlink ref="C5" r:id="rId4" xr:uid="{3BF8D633-F802-49D9-B215-C648CC6FE3D4}"/>
+    <hyperlink ref="C2" r:id="rId5" xr:uid="{EA84326D-6655-41E7-8734-36E1D746AFF9}"/>
+    <hyperlink ref="D2" r:id="rId6" xr:uid="{123A9953-D95A-4EE1-AD2F-223F45CCAED9}"/>
+    <hyperlink ref="D4" r:id="rId7" xr:uid="{E5B16B55-96AC-4978-AE33-0A830FCFE43C}"/>
+    <hyperlink ref="C4" r:id="rId8" xr:uid="{FF2B7FAD-E4CF-4B3E-AEE5-C270161AF49A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1014,7 +1051,7 @@
         <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -1074,10 +1111,10 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
